--- a/templates/mirror_inv_ss.xlsx
+++ b/templates/mirror_inv_ss.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/barrisol-calculator/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C2923F-C6CB-C54B-97A8-98E0B88342C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52535C6D-39CD-2C45-B582-97274E131F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{05935AE4-5CBA-6546-A82B-83CF6BB7C317}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="247">
   <si>
     <t>Outward Inventory Sheet</t>
   </si>
@@ -751,13 +751,40 @@
   </si>
   <si>
     <t>AC-GN-AK</t>
+  </si>
+  <si>
+    <t>AC-GN-SC</t>
+  </si>
+  <si>
+    <t>SCISSORS</t>
+  </si>
+  <si>
+    <t>AC-GN-CT</t>
+  </si>
+  <si>
+    <t>CELLO TAPE 75MM</t>
+  </si>
+  <si>
+    <t>AC-GN-PR</t>
+  </si>
+  <si>
+    <t>PAPER CUTTER</t>
+  </si>
+  <si>
+    <t>AC-GN-BP</t>
+  </si>
+  <si>
+    <t>CUTTER BLADE PACKET</t>
+  </si>
+  <si>
+    <t>SELECT MORE ACCESSORIES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -800,7 +827,8 @@
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val=".AppleSystemUIFont"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -823,7 +851,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -846,73 +874,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -927,39 +893,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1297,53 +1252,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E4533C-4F84-FE4D-9075-115EF828ACAF}">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="4" customWidth="1"/>
-    <col min="5" max="6" width="19.1640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14" style="4" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="21.1640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="28" style="4" customWidth="1"/>
-    <col min="12" max="12" width="23.1640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="31.33203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="10" customWidth="1"/>
+    <col min="5" max="6" width="19.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="14" style="10" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="21.1640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="28" style="10" customWidth="1"/>
+    <col min="12" max="12" width="23.1640625" style="7" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="32" customHeight="1">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="13"/>
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14"/>
       <c r="K1" s="14"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="27" customHeight="1">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1379,933 +1334,964 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="9" t="str">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A4" s="8" t="str">
         <f>VLOOKUP(B4, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>BR-3805-PS-03</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>3050</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="10">
         <f>ROUNDUP(D4*IF(H4="m", 0.05, IF(H4="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="10">
         <f>D4+E4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="10">
         <f>IF(ISBLANK(C4), F4,ROUND(((C4*F4)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="9" t="str">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A5" s="8" t="str">
         <f>VLOOKUP(B5, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>BR-3805-PE-02</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>3050</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="10">
         <f t="shared" ref="E5:E55" si="0">ROUNDUP(D5*IF(H5="m", 0.05, IF(H5="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="10">
         <f t="shared" ref="F5:F55" si="1">D5+E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="10">
         <f t="shared" ref="G5:G55" si="2">IF(ISBLANK(C5), F5,ROUND(((C5*F5)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="9" t="str">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A6" s="8" t="str">
         <f>VLOOKUP(B6, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>BR-3805-PP-02</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>3050</v>
       </c>
-      <c r="E6" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="9" t="str">
+      <c r="E6" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="str">
         <f>VLOOKUP(B7, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-AS</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>2440</v>
       </c>
-      <c r="E7" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="9" t="str">
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A8" s="8" t="str">
         <f>VLOOKUP(B8, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>RT-3825-01</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="E8" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="9" t="str">
+      <c r="C8" s="8"/>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A9" s="8" t="str">
         <f>VLOOKUP(B9, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-PC</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="E9" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="9" t="str">
+      <c r="C9" s="8"/>
+      <c r="E9" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A10" s="8" t="str">
         <f>VLOOKUP(B10, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-TA</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="E10" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="9" t="str">
+      <c r="C10" s="8"/>
+      <c r="E10" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A11" s="8" t="str">
         <f>VLOOKUP(B11, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-SA</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="E11" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="str">
+      <c r="C11" s="8"/>
+      <c r="E11" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A12" s="8" t="str">
         <f>VLOOKUP(B12, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-SC-SD19</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="E12" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="9" t="str">
+      <c r="C12" s="8"/>
+      <c r="E12" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A13" s="8" t="str">
         <f>VLOOKUP(B13, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-RV-0006</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="E13" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="9" t="str">
+      <c r="C13" s="8"/>
+      <c r="E13" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A14" s="8" t="str">
         <f>VLOOKUP(B14, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-SC-AL05</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="E14" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="9" t="str">
+      <c r="C14" s="8"/>
+      <c r="E14" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A15" s="8" t="str">
         <f>VLOOKUP(B15, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-AK</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="E15" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="9" t="str">
+      <c r="C15" s="8"/>
+      <c r="E15" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A16" s="8" t="str">
         <f>VLOOKUP(B16, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-TP</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="E16" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9" t="str">
+      <c r="C16" s="8"/>
+      <c r="E16" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="8" t="str">
         <f>VLOOKUP(B17, ACCESSORIES!A:B, 2, FALSE)</f>
         <v>AC-GN-LA</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="E18" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="E19" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="E20" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="E21" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="E22" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="E23" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="E24" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="E25" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="E26" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="E27" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="E28" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="E29" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="E30" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="E31" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="E32" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="5:7">
-      <c r="E33" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="5:7">
-      <c r="E34" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="5:7">
-      <c r="E35" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="5:7">
-      <c r="E36" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="5:7">
-      <c r="E37" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="5:7">
-      <c r="E38" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="5:7">
-      <c r="E39" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="5:7">
-      <c r="E40" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="5:7">
-      <c r="E41" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="5:7">
-      <c r="E42" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="5:7">
-      <c r="E43" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="5:7">
-      <c r="E44" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="5:7">
-      <c r="E45" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="5:7">
-      <c r="E46" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="5:7">
-      <c r="E47" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="5:7">
-      <c r="E48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="5:7">
-      <c r="E49" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="5:7">
-      <c r="E50" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="5:7">
-      <c r="E51" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="5:7">
-      <c r="E52" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="5:7">
-      <c r="E53" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="5:7">
-      <c r="E54" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="5:7">
-      <c r="E55" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="5:7">
-      <c r="E56" s="4">
+      <c r="E17" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A19" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A21" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A22" s="8" t="e">
+        <f>VLOOKUP(B22, ACCESSORIES!A:B, 2, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E23" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E24" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E25" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E26" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E27" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E28" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E29" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E30" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E31" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E32" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E33" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E34" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E35" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E36" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E37" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E38" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E39" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E40" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E41" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E42" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E43" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E44" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E45" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E46" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E47" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E48" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E49" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E50" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E51" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E52" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E53" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E54" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E55" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E56" s="10">
         <f t="shared" ref="E56:E61" si="3">ROUNDUP(D56*IF(H56="m", 0.05, IF(H56="pcs", 0.1, 0.05)), 0)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="10">
         <f t="shared" ref="F56:F61" si="4">D56+E56</f>
         <v>0</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="10">
         <f t="shared" ref="G56:G61" si="5">IF(ISBLANK(C56), F56,ROUND(((C56*F56)/1000), 2))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:7">
-      <c r="E57" s="4">
+    <row r="57" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E57" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="5:7">
-      <c r="E58" s="4">
+    <row r="58" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E58" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="5:7">
-      <c r="E59" s="4">
+    <row r="59" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E59" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G59" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="5:7">
-      <c r="E60" s="4">
+    <row r="60" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E60" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G60" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="5:7">
-      <c r="E61" s="4">
+    <row r="61" spans="5:7" x14ac:dyDescent="0.15">
+      <c r="E61" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2321,24 +2307,30 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0982DCEB-A7D6-AC4F-860F-6646DE633BC6}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$112:$A$113</xm:f>
+            <xm:f>ACCESSORIES!$A$28:$A$29</xm:f>
           </x14:formula1>
           <xm:sqref>B8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{48205412-0FFA-C944-91AC-BE3624C871DF}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$26:$A$29</xm:f>
+            <xm:f>ACCESSORIES!$A$25:$A$28</xm:f>
           </x14:formula1>
           <xm:sqref>B12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1195C7CA-E762-F948-AD4D-99325F0A01B8}">
           <x14:formula1>
-            <xm:f>ACCESSORIES!$A$24:$A$25</xm:f>
+            <xm:f>ACCESSORIES!$A$23:$A$24</xm:f>
           </x14:formula1>
           <xm:sqref>B14</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5585BB09-1C9F-9D4B-8478-2A4E5257E2EB}">
+          <x14:formula1>
+            <xm:f>ACCESSORIES!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B22</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2349,13 +2341,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED1BDD3-06DA-CA42-BD86-FA2419A38AFC}">
   <dimension ref="A1:B116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
@@ -2363,7 +2355,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -2371,7 +2363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
@@ -2379,7 +2371,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>21</v>
       </c>
@@ -2387,7 +2379,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
@@ -2395,7 +2387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
@@ -2403,7 +2395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
@@ -2411,7 +2403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -2419,7 +2411,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
@@ -2427,7 +2419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
@@ -2435,7 +2427,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -2443,7 +2435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
@@ -2451,7 +2443,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
@@ -2459,831 +2451,832 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="5" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="5" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="5" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B35" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="5" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="5" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="5" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="5" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="5" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="5" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="5" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="5" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="5" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="5" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="5" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="5" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="5" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="5" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="5" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="5" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="5" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="5" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="5" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="5" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="5" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B64" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="5" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="5" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B66" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="5" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="5" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B68" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="5" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B69" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="5" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B70" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="5" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B71" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="5" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B72" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="5" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B73" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="5" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B74" s="5" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="5" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B75" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="5" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B76" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="5" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B77" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="5" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B78" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="5" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B79" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="5" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B80" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="5" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B81" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="5" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B82" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="5" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B83" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="5" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B84" s="5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="5" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B85" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="5" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B86" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="5" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B87" s="5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="5" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B88" s="5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="5" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B89" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="5" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B90" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="5" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B91" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="5" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B92" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="5" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B93" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="5" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B94" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="5" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B95" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="5" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B96" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="5" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B97" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="5" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B98" s="5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="5" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B99" s="5" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="5" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B100" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="5" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B101" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="5" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B102" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="5" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B103" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="5" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B104" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="5" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B105" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="5" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B106" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="5" t="s">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B107" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="5" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B108" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="5" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B109" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="5" t="s">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B110" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="5" t="s">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B111" s="5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="5" t="s">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B112" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="5" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B113" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="5" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B114" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="5" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B115" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="5" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B116" s="5" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="17">
-      <c r="A112" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" ht="17">
-      <c r="A113" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>